--- a/Product_Source/电动葫芦排绳器0.5吨1吨2吨16吨10吨5吨3吨导绳器钢丝绳吊葫芦/电动葫芦排绳器0.5吨1吨2吨16吨10吨5吨3吨导绳器钢丝绳吊葫芦.xlsx
+++ b/Product_Source/电动葫芦排绳器0.5吨1吨2吨16吨10吨5吨3吨导绳器钢丝绳吊葫芦/电动葫芦排绳器0.5吨1吨2吨16吨10吨5吨3吨导绳器钢丝绳吊葫芦.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\AA_Project\Enterprise_Web\hntzs\Data\1688\电动葫芦排绳器0.5吨1吨2吨16吨10吨5吨3吨导绳器钢丝绳吊葫芦\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\AA_Project\Enterprise_Web\hntzs\technological-trappist\Product_Source\电动葫芦排绳器0.5吨1吨2吨16吨10吨5吨3吨导绳器钢丝绳吊葫芦\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA2977E0-9E5C-4A24-BFAD-6F08204BA332}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97825789-B104-4DFD-ABF3-32FD252CB7B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14400" yWindow="0" windowWidth="14400" windowHeight="15600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="44">
   <si>
     <t>产品规格</t>
   </si>
@@ -52,9 +52,6 @@
   </si>
   <si>
     <t>价格 | 库存(台)</t>
-  </si>
-  <si>
-    <t>进货数量</t>
   </si>
   <si>
     <t>0.5T</t>
@@ -490,7 +487,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.125" bestFit="1" customWidth="1"/>
@@ -503,7 +500,7 @@
     <col min="9" max="9" width="13.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -531,25 +528,22 @@
       <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
+      <c r="B3" t="s">
         <v>10</v>
       </c>
-      <c r="B3" t="s">
-        <v>11</v>
-      </c>
       <c r="C3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F3">
         <v>13</v>
@@ -564,21 +558,21 @@
         <v>18.02</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" t="s">
         <v>15</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" t="s">
         <v>16</v>
-      </c>
-      <c r="C4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" t="s">
-        <v>17</v>
       </c>
       <c r="F4">
         <v>13</v>
@@ -593,21 +587,21 @@
         <v>21.2</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" t="s">
         <v>18</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" t="s">
         <v>19</v>
-      </c>
-      <c r="C5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E5" t="s">
-        <v>20</v>
       </c>
       <c r="F5">
         <v>13</v>
@@ -622,21 +616,21 @@
         <v>22.26</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
         <v>21</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" t="s">
         <v>22</v>
-      </c>
-      <c r="C6" t="s">
-        <v>12</v>
-      </c>
-      <c r="D6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E6" t="s">
-        <v>23</v>
       </c>
       <c r="F6">
         <v>13</v>
@@ -651,21 +645,21 @@
         <v>23.32</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" t="s">
         <v>24</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7" t="s">
         <v>25</v>
-      </c>
-      <c r="C7" t="s">
-        <v>12</v>
-      </c>
-      <c r="D7" t="s">
-        <v>13</v>
-      </c>
-      <c r="E7" t="s">
-        <v>26</v>
       </c>
       <c r="F7">
         <v>13</v>
@@ -680,21 +674,21 @@
         <v>27.56</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" t="s">
         <v>27</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8" t="s">
         <v>28</v>
-      </c>
-      <c r="C8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E8" t="s">
-        <v>29</v>
       </c>
       <c r="F8">
         <v>13</v>
@@ -709,21 +703,21 @@
         <v>90.1</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B9" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E9" t="s">
         <v>16</v>
-      </c>
-      <c r="C9" t="s">
-        <v>12</v>
-      </c>
-      <c r="D9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E9" t="s">
-        <v>17</v>
       </c>
       <c r="F9">
         <v>13</v>
@@ -738,21 +732,21 @@
         <v>63.6</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" t="s">
+        <v>11</v>
+      </c>
+      <c r="D10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E10" t="s">
         <v>19</v>
-      </c>
-      <c r="C10" t="s">
-        <v>12</v>
-      </c>
-      <c r="D10" t="s">
-        <v>13</v>
-      </c>
-      <c r="E10" t="s">
-        <v>20</v>
       </c>
       <c r="F10">
         <v>13</v>
@@ -767,21 +761,21 @@
         <v>79.5</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B11" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E11" t="s">
         <v>22</v>
-      </c>
-      <c r="C11" t="s">
-        <v>12</v>
-      </c>
-      <c r="D11" t="s">
-        <v>13</v>
-      </c>
-      <c r="E11" t="s">
-        <v>23</v>
       </c>
       <c r="F11">
         <v>13</v>
@@ -796,21 +790,21 @@
         <v>84.8</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" t="s">
+        <v>11</v>
+      </c>
+      <c r="D12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E12" t="s">
         <v>25</v>
-      </c>
-      <c r="C12" t="s">
-        <v>12</v>
-      </c>
-      <c r="D12" t="s">
-        <v>13</v>
-      </c>
-      <c r="E12" t="s">
-        <v>26</v>
       </c>
       <c r="F12">
         <v>13</v>
@@ -825,21 +819,21 @@
         <v>116.6</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B13" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" t="s">
+        <v>11</v>
+      </c>
+      <c r="D13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E13" t="s">
         <v>28</v>
-      </c>
-      <c r="C13" t="s">
-        <v>12</v>
-      </c>
-      <c r="D13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E13" t="s">
-        <v>29</v>
       </c>
       <c r="F13">
         <v>13</v>
@@ -854,21 +848,21 @@
         <v>286.2</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
+        <v>34</v>
+      </c>
+      <c r="B14" t="s">
         <v>35</v>
       </c>
-      <c r="B14" t="s">
-        <v>36</v>
-      </c>
       <c r="C14" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D14" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F14">
         <v>13</v>
@@ -883,21 +877,21 @@
         <v>339.2</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B15" t="s">
+        <v>21</v>
+      </c>
+      <c r="C15" t="s">
+        <v>11</v>
+      </c>
+      <c r="D15" t="s">
+        <v>12</v>
+      </c>
+      <c r="E15" t="s">
         <v>22</v>
-      </c>
-      <c r="C15" t="s">
-        <v>12</v>
-      </c>
-      <c r="D15" t="s">
-        <v>13</v>
-      </c>
-      <c r="E15" t="s">
-        <v>23</v>
       </c>
       <c r="F15">
         <v>13</v>
@@ -912,21 +906,21 @@
         <v>148.4</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B16" t="s">
+        <v>24</v>
+      </c>
+      <c r="C16" t="s">
+        <v>11</v>
+      </c>
+      <c r="D16" t="s">
+        <v>12</v>
+      </c>
+      <c r="E16" t="s">
         <v>25</v>
-      </c>
-      <c r="C16" t="s">
-        <v>12</v>
-      </c>
-      <c r="D16" t="s">
-        <v>13</v>
-      </c>
-      <c r="E16" t="s">
-        <v>26</v>
       </c>
       <c r="F16">
         <v>13</v>
@@ -943,19 +937,19 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D17" t="s">
+        <v>12</v>
+      </c>
+      <c r="E17" t="s">
         <v>28</v>
-      </c>
-      <c r="C17" t="s">
-        <v>12</v>
-      </c>
-      <c r="D17" t="s">
-        <v>13</v>
-      </c>
-      <c r="E17" t="s">
-        <v>29</v>
       </c>
       <c r="F17">
         <v>13</v>
@@ -972,19 +966,19 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
+        <v>39</v>
+      </c>
+      <c r="B18" t="s">
         <v>40</v>
       </c>
-      <c r="B18" t="s">
-        <v>41</v>
-      </c>
       <c r="C18" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D18" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E18" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F18">
         <v>13</v>
@@ -1001,19 +995,19 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B19" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C19" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D19" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E19" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F19">
         <v>13</v>
@@ -1030,19 +1024,19 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
+        <v>42</v>
+      </c>
+      <c r="B20" t="s">
         <v>43</v>
       </c>
-      <c r="B20" t="s">
-        <v>44</v>
-      </c>
       <c r="C20" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D20" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E20" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F20">
         <v>13</v>
